--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.69199154297763</v>
+        <v>2.387448625733865</v>
       </c>
       <c r="D2" t="n">
-        <v>14.72383275531162</v>
+        <v>2.392622822738139</v>
       </c>
       <c r="E2" t="n">
-        <v>1.366080723981826</v>
+        <v>0.2219881176470468</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7648445450746418</v>
+        <v>0.1242872385746294</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.46375964898948</v>
+        <v>2.837860942960791</v>
       </c>
       <c r="D3" t="n">
-        <v>16.13119059835018</v>
+        <v>2.621318472231905</v>
       </c>
       <c r="E3" t="n">
-        <v>1.366080723981826</v>
+        <v>0.2219881176470468</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7648445450746418</v>
+        <v>0.1242872385746294</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.70138125499057</v>
+        <v>2.876474453935967</v>
       </c>
       <c r="D4" t="n">
-        <v>16.49846929868872</v>
+        <v>2.681001261036918</v>
       </c>
       <c r="E4" t="n">
-        <v>1.366080723981826</v>
+        <v>0.2219881176470468</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7648445450746418</v>
+        <v>0.1242872385746294</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
